--- a/dashboard/public/starter-pack/08_Price_to_Win_Toolkit/FLK_08_Indirect_Rate_Calculator.xlsx
+++ b/dashboard/public/starter-pack/08_Price_to_Win_Toolkit/FLK_08_Indirect_Rate_Calculator.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Direct Labor" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Cost Pools" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Rate Summary" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Help" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Direct Labor" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Cost Pools" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Rate Summary" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Help" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="ClearanceLevel">Lists!$A$2:$A$6</definedName>
+    <definedName name="DirectIndirect">Lists!$B$2:$B$3</definedName>
     <definedName name="DL_Base">'Direct Labor'!$D$16</definedName>
     <definedName name="Indirect_Labor_Total">'Direct Labor'!$D$24</definedName>
     <definedName name="Fringe_Pool">'Cost Pools'!$B$17</definedName>
@@ -22,7 +25,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="220">
+  <si>
+    <t>Clearance Level</t>
+  </si>
+  <si>
+    <t>Direct or Indirect</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Public Trust</t>
+  </si>
+  <si>
+    <t>Indirect</t>
+  </si>
+  <si>
+    <t>Secret</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>TS/SCI</t>
+  </si>
   <si>
     <t>FEDERAL LEAD KIT — Indirect Rate Calculator</t>
   </si>
@@ -180,18 +210,9 @@
     <t xml:space="preserve">  Program Manager</t>
   </si>
   <si>
-    <t>Secret</t>
-  </si>
-  <si>
-    <t>Direct</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Senior Systems Engineer</t>
   </si>
   <si>
-    <t>TS/SCI</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Systems Engineer (Mid)</t>
   </si>
   <si>
@@ -201,9 +222,6 @@
     <t xml:space="preserve">  Software Developer (Mid)</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Data Analyst</t>
   </si>
   <si>
@@ -232,9 +250,6 @@
   </si>
   <si>
     <t xml:space="preserve">  Project Controls / Scheduler</t>
-  </si>
-  <si>
-    <t>Indirect</t>
   </si>
   <si>
     <t xml:space="preserve">  HR Manager</t>
@@ -682,12 +697,21 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -780,12 +804,17 @@
       <name val="Consolas"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -920,90 +949,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1415,6 +1450,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1427,206 +1515,206 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>9</v>
+      <c r="A10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>12</v>
+      <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
+      <c r="A12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>18</v>
+      <c r="A13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>21</v>
+      <c r="B16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>23</v>
+      <c r="B17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>25</v>
+      <c r="B18" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>27</v>
+      <c r="B19" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>29</v>
+      <c r="B20" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" ht="30" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>32</v>
+      <c r="B23" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>34</v>
+      <c r="B24" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>36</v>
+      <c r="B25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>38</v>
+      <c r="B26" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1668,547 +1756,547 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="A2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>49</v>
+      <c r="A4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="20">
+      <c r="A6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="22">
         <v>145000</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="23">
         <v>1860</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="24">
         <f>IFERROR(D6/E6,0)</f>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="25">
         <f>D6*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="25">
         <f>D6+G6</f>
       </c>
-      <c r="I6" s="24"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="20">
+      <c r="A7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="22">
         <v>155000</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="23">
         <v>1860</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="24">
         <f>IFERROR(D7/E7,0)</f>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <f>D7*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="25">
         <f>D7+G7</f>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="20">
+      <c r="A8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="22">
         <v>115000</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="23">
         <v>1860</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="24">
         <f>IFERROR(D8/E8,0)</f>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="25">
         <f>D8*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="25">
         <f>D8+G8</f>
       </c>
-      <c r="I8" s="24"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="20">
+      <c r="A9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="22">
         <v>140000</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="23">
         <v>1860</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="24">
         <f>IFERROR(D9/E9,0)</f>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="25">
         <f>D9*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="25">
         <f>D9+G9</f>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="20">
+      <c r="A10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="22">
         <v>105000</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="23">
         <v>1860</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>IFERROR(D10/E10,0)</f>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="25">
         <f>D10*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="25">
         <f>D10+G10</f>
       </c>
-      <c r="I10" s="24"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="20">
+      <c r="A11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="22">
         <v>95000</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="23">
         <v>1860</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="24">
         <f>IFERROR(D11/E11,0)</f>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="25">
         <f>D11*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="25">
         <f>D11+G11</f>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="20">
+      <c r="A12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="22">
         <v>78000</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="23">
         <v>1860</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="24">
         <f>IFERROR(D12/E12,0)</f>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <f>D12*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="25">
         <f>D12+G12</f>
       </c>
-      <c r="I12" s="24"/>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="20">
+      <c r="A13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="22">
         <v>110000</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="23">
         <v>1860</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="24">
         <f>IFERROR(D13/E13,0)</f>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="25">
         <f>D13*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="25">
         <f>D13+G13</f>
       </c>
-      <c r="I13" s="24"/>
+      <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="20">
+      <c r="A14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="22">
         <v>72000</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="23">
         <v>1860</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="24">
         <f>IFERROR(D14/E14,0)</f>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="25">
         <f>D14*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="25">
         <f>D14+G14</f>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="20">
+      <c r="A15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="22">
         <v>90000</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="23">
         <v>960</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="24">
         <f>IFERROR(D15/E15,0)</f>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="25">
         <f>D15*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="25">
         <f>D15+G15</f>
       </c>
-      <c r="I15" s="24"/>
+      <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="26">
+      <c r="A16" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="28">
         <f>SUM(D6:D15)</f>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <f>SUM(E6:E15)</f>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="30">
         <f>IFERROR(D16/E16,0)</f>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="28">
         <f>SUM(G6:G15)</f>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="28">
         <f>SUM(H6:H15)</f>
       </c>
-      <c r="I16" s="25" t="s">
-        <v>67</v>
+      <c r="I16" s="27" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="A18" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="20">
+      <c r="A19" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="22">
         <v>88000</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="23">
         <v>2080</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="24">
         <f>IFERROR(D19/E19,0)</f>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="25">
         <f>D19*'Rate Summary'!$D$10</f>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="25">
         <f>D19+G19</f>
       </c>
-      <c r="I19" s="24"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="22">
+        <v>95000</v>
+      </c>
+      <c r="E20" s="23">
+        <v>2080</v>
+      </c>
+      <c r="F20" s="24">
+        <f>IFERROR(D20/E20,0)</f>
+      </c>
+      <c r="G20" s="25">
+        <f>D20*'Rate Summary'!$D$10</f>
+      </c>
+      <c r="H20" s="25">
+        <f>D20+G20</f>
+      </c>
+      <c r="I20" s="26"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="22">
+        <v>125000</v>
+      </c>
+      <c r="E21" s="23">
+        <v>2080</v>
+      </c>
+      <c r="F21" s="24">
+        <f>IFERROR(D21/E21,0)</f>
+      </c>
+      <c r="G21" s="25">
+        <f>D21*'Rate Summary'!$D$10</f>
+      </c>
+      <c r="H21" s="25">
+        <f>D21+G21</f>
+      </c>
+      <c r="I21" s="26"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="22">
+        <v>92000</v>
+      </c>
+      <c r="E22" s="23">
+        <v>2080</v>
+      </c>
+      <c r="F22" s="24">
+        <f>IFERROR(D22/E22,0)</f>
+      </c>
+      <c r="G22" s="25">
+        <f>D22*'Rate Summary'!$D$10</f>
+      </c>
+      <c r="H22" s="25">
+        <f>D22+G22</f>
+      </c>
+      <c r="I22" s="26"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="22">
+        <v>68000</v>
+      </c>
+      <c r="E23" s="23">
+        <v>2080</v>
+      </c>
+      <c r="F23" s="24">
+        <f>IFERROR(D23/E23,0)</f>
+      </c>
+      <c r="G23" s="25">
+        <f>D23*'Rate Summary'!$D$10</f>
+      </c>
+      <c r="H23" s="25">
+        <f>D23+G23</f>
+      </c>
+      <c r="I23" s="26"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="20">
-        <v>95000</v>
-      </c>
-      <c r="E20" s="21">
-        <v>2080</v>
-      </c>
-      <c r="F20" s="22">
-        <f>IFERROR(D20/E20,0)</f>
-      </c>
-      <c r="G20" s="23">
-        <f>D20*'Rate Summary'!$D$10</f>
-      </c>
-      <c r="H20" s="23">
-        <f>D20+G20</f>
-      </c>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="20">
-        <v>125000</v>
-      </c>
-      <c r="E21" s="21">
-        <v>2080</v>
-      </c>
-      <c r="F21" s="22">
-        <f>IFERROR(D21/E21,0)</f>
-      </c>
-      <c r="G21" s="23">
-        <f>D21*'Rate Summary'!$D$10</f>
-      </c>
-      <c r="H21" s="23">
-        <f>D21+G21</f>
-      </c>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="20">
-        <v>92000</v>
-      </c>
-      <c r="E22" s="21">
-        <v>2080</v>
-      </c>
-      <c r="F22" s="22">
-        <f>IFERROR(D22/E22,0)</f>
-      </c>
-      <c r="G22" s="23">
-        <f>D22*'Rate Summary'!$D$10</f>
-      </c>
-      <c r="H22" s="23">
-        <f>D22+G22</f>
-      </c>
-      <c r="I22" s="24"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="20">
-        <v>68000</v>
-      </c>
-      <c r="E23" s="21">
-        <v>2080</v>
-      </c>
-      <c r="F23" s="22">
-        <f>IFERROR(D23/E23,0)</f>
-      </c>
-      <c r="G23" s="23">
-        <f>D23*'Rate Summary'!$D$10</f>
-      </c>
-      <c r="H23" s="23">
-        <f>D23+G23</f>
-      </c>
-      <c r="I23" s="24"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="26">
+      <c r="C24" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="28">
         <f>SUM(D19:D23)</f>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="29">
         <f>SUM(E19:E23)</f>
       </c>
-      <c r="F24" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="26">
+      <c r="F24" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="28">
         <f>SUM(G19:G23)</f>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="28">
         <f>SUM(H19:H23)</f>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>76</v>
+      <c r="I24" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2220,22 +2308,22 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="B10:B15">
-      <formula1>"None,Public Trust,Secret,TS,TS/SCI"</formula1>
+      <formula1>ClearanceLevel</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B19:B23">
-      <formula1>"None,Public Trust,Secret,TS,TS/SCI"</formula1>
+      <formula1>ClearanceLevel</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B6:B15">
-      <formula1>"None,Public Trust,Secret,TS,TS/SCI"</formula1>
+      <formula1>ClearanceLevel</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C10:C15">
-      <formula1>"Direct,Indirect"</formula1>
+      <formula1>DirectIndirect</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C19:C23">
-      <formula1>"Direct,Indirect"</formula1>
+      <formula1>DirectIndirect</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C6:C15">
-      <formula1>"Direct,Indirect"</formula1>
+      <formula1>DirectIndirect</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2247,7 +2335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2261,390 +2349,390 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="20">
+      <c r="A5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="22">
         <v>75000</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="31"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="22">
         <v>18000</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="22">
         <v>600</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="22">
         <v>8500</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="22">
         <v>95000</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="22">
         <v>11000</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="22">
         <v>42000</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="31"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="22">
         <v>56000</v>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="22">
         <v>38000</v>
       </c>
-      <c r="C13" s="29"/>
+      <c r="C13" s="31"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="22">
         <v>7500</v>
       </c>
-      <c r="C14" s="29"/>
+      <c r="C14" s="31"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="22">
         <v>8500</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="31"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="22">
         <v>5000</v>
       </c>
-      <c r="C16" s="29"/>
+      <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="26">
+      <c r="A17" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="28">
         <f>SUM(B5:B16)</f>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>93</v>
+      <c r="C17" s="27" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="A19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="23">
+      <c r="A20" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="25">
         <f>Indirect_Labor_Total</f>
       </c>
-      <c r="C20" s="30" t="s">
-        <v>96</v>
+      <c r="C20" s="32" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="23">
+      <c r="A21" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="25">
         <f>Indirect_Labor_Total*'Rate Summary'!$D$10</f>
       </c>
-      <c r="C21" s="30" t="s">
-        <v>96</v>
+      <c r="C21" s="32" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="20">
+      <c r="A22" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="22">
         <v>96000</v>
       </c>
-      <c r="C22" s="29"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="20">
+      <c r="A23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="22">
         <v>28000</v>
       </c>
-      <c r="C23" s="29"/>
+      <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="20">
+      <c r="A24" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="22">
         <v>12000</v>
       </c>
-      <c r="C24" s="29"/>
+      <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="20">
+      <c r="A25" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="22">
         <v>14000</v>
       </c>
-      <c r="C25" s="29"/>
+      <c r="C25" s="31"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="22">
         <v>9500</v>
       </c>
-      <c r="C26" s="29"/>
+      <c r="C26" s="31"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="20">
+      <c r="A27" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="22">
         <v>8000</v>
       </c>
-      <c r="C27" s="29"/>
+      <c r="C27" s="31"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="20">
+      <c r="A28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="22">
         <v>6000</v>
       </c>
-      <c r="C28" s="29"/>
+      <c r="C28" s="31"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="26">
+      <c r="A29" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="28">
         <f>SUM(B20:B28)</f>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>106</v>
+      <c r="C29" s="27" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="A31" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="20">
+      <c r="A32" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="22">
         <v>220000</v>
       </c>
-      <c r="C32" s="29"/>
+      <c r="C32" s="31"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="20">
+      <c r="A33" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="22">
         <v>66000</v>
       </c>
-      <c r="C33" s="29"/>
+      <c r="C33" s="31"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="20">
+      <c r="A34" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="22">
         <v>38000</v>
       </c>
-      <c r="C34" s="29"/>
+      <c r="C34" s="31"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B35" s="20">
+      <c r="A35" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="22">
         <v>22000</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="31"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="20">
+      <c r="A36" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="22">
         <v>45000</v>
       </c>
-      <c r="C36" s="29"/>
+      <c r="C36" s="31"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="20">
+      <c r="A37" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="22">
         <v>18000</v>
       </c>
-      <c r="C37" s="29"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="20">
+      <c r="A38" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="22">
         <v>24000</v>
       </c>
-      <c r="C38" s="29"/>
+      <c r="C38" s="31"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="20">
+      <c r="A39" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="22">
         <v>9000</v>
       </c>
-      <c r="C39" s="29"/>
+      <c r="C39" s="31"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="20">
+      <c r="A40" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="22">
         <v>28000</v>
       </c>
-      <c r="C40" s="29"/>
+      <c r="C40" s="31"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" s="20">
+      <c r="A41" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="22">
         <v>14000</v>
       </c>
-      <c r="C41" s="29"/>
+      <c r="C41" s="31"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="22">
         <v>32000</v>
       </c>
-      <c r="C42" s="29"/>
+      <c r="C42" s="31"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="20">
+      <c r="A43" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" s="22">
         <v>6000</v>
       </c>
-      <c r="C43" s="29"/>
+      <c r="C43" s="31"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" s="26">
+      <c r="A44" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="28">
         <f>SUM(B32:B43)</f>
       </c>
-      <c r="C44" s="25" t="s">
-        <v>121</v>
+      <c r="C44" s="27" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2679,519 +2767,519 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="A2" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="31">
+      <c r="B6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="33">
         <v>0.08</v>
       </c>
-      <c r="E6" s="30" t="s">
-        <v>126</v>
+      <c r="E6" s="32" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="31">
+      <c r="B7" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="33">
         <v>0.03</v>
       </c>
-      <c r="E7" s="30" t="s">
-        <v>128</v>
+      <c r="E7" s="32" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="31" t="s">
+      <c r="B8" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="25">
+        <f>DL_Base</f>
+      </c>
+      <c r="D10" s="34">
+        <f>IF(ISNUMBER(D8),D8,IFERROR(Fringe_Pool/DL_Base,0))</f>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="25">
+        <f>OH_Pool</f>
+      </c>
+      <c r="D11" s="34">
+        <f>IFERROR(OH_Pool/DL_Base,0)</f>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="25">
+        <f>DL_Base*(1+D10+D11)</f>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="25">
+        <f>GA_Pool</f>
+      </c>
+      <c r="D13" s="34">
+        <f>IFERROR(GA_Pool/C12,0)</f>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="35">
+        <f>(1+D10)*(1+D11)*(1+D13)</f>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="35">
+        <f>D16*(1+D6)</f>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="22">
+        <v>145000</v>
+      </c>
+      <c r="D21" s="24">
+        <f>C21/1860</f>
+      </c>
+      <c r="E21" s="24">
+        <f>D21*(1+$D$10)</f>
+      </c>
+      <c r="F21" s="24">
+        <f>E21*(1+$D$11)</f>
+      </c>
+      <c r="G21" s="24">
+        <f>F21*(1+$D$13)</f>
+      </c>
+      <c r="H21" s="36">
+        <f>G21*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="22">
+        <v>155000</v>
+      </c>
+      <c r="D22" s="24">
+        <f>C22/1860</f>
+      </c>
+      <c r="E22" s="24">
+        <f>D22*(1+$D$10)</f>
+      </c>
+      <c r="F22" s="24">
+        <f>E22*(1+$D$11)</f>
+      </c>
+      <c r="G22" s="24">
+        <f>F22*(1+$D$13)</f>
+      </c>
+      <c r="H22" s="36">
+        <f>G22*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="22">
+        <v>115000</v>
+      </c>
+      <c r="D23" s="24">
+        <f>C23/1860</f>
+      </c>
+      <c r="E23" s="24">
+        <f>D23*(1+$D$10)</f>
+      </c>
+      <c r="F23" s="24">
+        <f>E23*(1+$D$11)</f>
+      </c>
+      <c r="G23" s="24">
+        <f>F23*(1+$D$13)</f>
+      </c>
+      <c r="H23" s="36">
+        <f>G23*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="22">
+        <v>140000</v>
+      </c>
+      <c r="D24" s="24">
+        <f>C24/1860</f>
+      </c>
+      <c r="E24" s="24">
+        <f>D24*(1+$D$10)</f>
+      </c>
+      <c r="F24" s="24">
+        <f>E24*(1+$D$11)</f>
+      </c>
+      <c r="G24" s="24">
+        <f>F24*(1+$D$13)</f>
+      </c>
+      <c r="H24" s="36">
+        <f>G24*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="22">
+        <v>105000</v>
+      </c>
+      <c r="D25" s="24">
+        <f>C25/1860</f>
+      </c>
+      <c r="E25" s="24">
+        <f>D25*(1+$D$10)</f>
+      </c>
+      <c r="F25" s="24">
+        <f>E25*(1+$D$11)</f>
+      </c>
+      <c r="G25" s="24">
+        <f>F25*(1+$D$13)</f>
+      </c>
+      <c r="H25" s="36">
+        <f>G25*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="22">
+        <v>95000</v>
+      </c>
+      <c r="D26" s="24">
+        <f>C26/1860</f>
+      </c>
+      <c r="E26" s="24">
+        <f>D26*(1+$D$10)</f>
+      </c>
+      <c r="F26" s="24">
+        <f>E26*(1+$D$11)</f>
+      </c>
+      <c r="G26" s="24">
+        <f>F26*(1+$D$13)</f>
+      </c>
+      <c r="H26" s="36">
+        <f>G26*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="23">
-        <f>DL_Base</f>
-      </c>
-      <c r="D10" s="32">
-        <f>IF(ISNUMBER(D8),D8,IFERROR(Fringe_Pool/DL_Base,0))</f>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="23">
-        <f>OH_Pool</f>
-      </c>
-      <c r="D11" s="32">
-        <f>IFERROR(OH_Pool/DL_Base,0)</f>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="23">
-        <f>DL_Base*(1+D10+D11)</f>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="C27" s="22">
+        <v>78000</v>
+      </c>
+      <c r="D27" s="24">
+        <f>C27/1860</f>
+      </c>
+      <c r="E27" s="24">
+        <f>D27*(1+$D$10)</f>
+      </c>
+      <c r="F27" s="24">
+        <f>E27*(1+$D$11)</f>
+      </c>
+      <c r="G27" s="24">
+        <f>F27*(1+$D$13)</f>
+      </c>
+      <c r="H27" s="36">
+        <f>G27*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="22">
+        <v>110000</v>
+      </c>
+      <c r="D28" s="24">
+        <f>C28/1860</f>
+      </c>
+      <c r="E28" s="24">
+        <f>D28*(1+$D$10)</f>
+      </c>
+      <c r="F28" s="24">
+        <f>E28*(1+$D$11)</f>
+      </c>
+      <c r="G28" s="24">
+        <f>F28*(1+$D$13)</f>
+      </c>
+      <c r="H28" s="36">
+        <f>G28*(1+$D$6)</f>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="38">
+        <f>D10</f>
+      </c>
+      <c r="D33" s="39">
+        <v>0.25</v>
+      </c>
+      <c r="E33" s="39">
+        <v>0.35</v>
+      </c>
+      <c r="F33" s="40">
+        <f>IF(C33&lt;D33,"BELOW typical — investigate",IF(C33&gt;E33,"ABOVE typical — review","WITHIN typical range"))</f>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="23">
-        <f>GA_Pool</f>
-      </c>
-      <c r="D13" s="32">
-        <f>IFERROR(GA_Pool/C12,0)</f>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="33">
-        <f>(1+D10)*(1+D11)*(1+D13)</f>
-      </c>
-      <c r="E16" s="30" t="s">
+      <c r="C34" s="38">
+        <f>D11</f>
+      </c>
+      <c r="D34" s="39">
+        <v>0.1</v>
+      </c>
+      <c r="E34" s="39">
+        <v>0.25</v>
+      </c>
+      <c r="F34" s="40">
+        <f>IF(C34&lt;D34,"BELOW typical — investigate",IF(C34&gt;E34,"ABOVE typical — review","WITHIN typical range"))</f>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="33">
-        <f>D16*(1+D6)</f>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="20">
-        <v>145000</v>
-      </c>
-      <c r="D21" s="22">
-        <f>C21/1860</f>
-      </c>
-      <c r="E21" s="22">
-        <f>D21*(1+$D$10)</f>
-      </c>
-      <c r="F21" s="22">
-        <f>E21*(1+$D$11)</f>
-      </c>
-      <c r="G21" s="22">
-        <f>F21*(1+$D$13)</f>
-      </c>
-      <c r="H21" s="34">
-        <f>G21*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="20">
-        <v>155000</v>
-      </c>
-      <c r="D22" s="22">
-        <f>C22/1860</f>
-      </c>
-      <c r="E22" s="22">
-        <f>D22*(1+$D$10)</f>
-      </c>
-      <c r="F22" s="22">
-        <f>E22*(1+$D$11)</f>
-      </c>
-      <c r="G22" s="22">
-        <f>F22*(1+$D$13)</f>
-      </c>
-      <c r="H22" s="34">
-        <f>G22*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="20">
-        <v>115000</v>
-      </c>
-      <c r="D23" s="22">
-        <f>C23/1860</f>
-      </c>
-      <c r="E23" s="22">
-        <f>D23*(1+$D$10)</f>
-      </c>
-      <c r="F23" s="22">
-        <f>E23*(1+$D$11)</f>
-      </c>
-      <c r="G23" s="22">
-        <f>F23*(1+$D$13)</f>
-      </c>
-      <c r="H23" s="34">
-        <f>G23*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="20">
-        <v>140000</v>
-      </c>
-      <c r="D24" s="22">
-        <f>C24/1860</f>
-      </c>
-      <c r="E24" s="22">
-        <f>D24*(1+$D$10)</f>
-      </c>
-      <c r="F24" s="22">
-        <f>E24*(1+$D$11)</f>
-      </c>
-      <c r="G24" s="22">
-        <f>F24*(1+$D$13)</f>
-      </c>
-      <c r="H24" s="34">
-        <f>G24*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="20">
-        <v>105000</v>
-      </c>
-      <c r="D25" s="22">
-        <f>C25/1860</f>
-      </c>
-      <c r="E25" s="22">
-        <f>D25*(1+$D$10)</f>
-      </c>
-      <c r="F25" s="22">
-        <f>E25*(1+$D$11)</f>
-      </c>
-      <c r="G25" s="22">
-        <f>F25*(1+$D$13)</f>
-      </c>
-      <c r="H25" s="34">
-        <f>G25*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="20">
-        <v>95000</v>
-      </c>
-      <c r="D26" s="22">
-        <f>C26/1860</f>
-      </c>
-      <c r="E26" s="22">
-        <f>D26*(1+$D$10)</f>
-      </c>
-      <c r="F26" s="22">
-        <f>E26*(1+$D$11)</f>
-      </c>
-      <c r="G26" s="22">
-        <f>F26*(1+$D$13)</f>
-      </c>
-      <c r="H26" s="34">
-        <f>G26*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="20">
-        <v>78000</v>
-      </c>
-      <c r="D27" s="22">
-        <f>C27/1860</f>
-      </c>
-      <c r="E27" s="22">
-        <f>D27*(1+$D$10)</f>
-      </c>
-      <c r="F27" s="22">
-        <f>E27*(1+$D$11)</f>
-      </c>
-      <c r="G27" s="22">
-        <f>F27*(1+$D$13)</f>
-      </c>
-      <c r="H27" s="34">
-        <f>G27*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="20">
-        <v>110000</v>
-      </c>
-      <c r="D28" s="22">
-        <f>C28/1860</f>
-      </c>
-      <c r="E28" s="22">
-        <f>D28*(1+$D$10)</f>
-      </c>
-      <c r="F28" s="22">
-        <f>E28*(1+$D$11)</f>
-      </c>
-      <c r="G28" s="22">
-        <f>F28*(1+$D$13)</f>
-      </c>
-      <c r="H28" s="34">
-        <f>G28*(1+$D$6)</f>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="36">
-        <f>D10</f>
-      </c>
-      <c r="D33" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="E33" s="37">
-        <v>0.35</v>
-      </c>
-      <c r="F33" s="38">
-        <f>IF(C33&lt;D33,"BELOW typical — investigate",IF(C33&gt;E33,"ABOVE typical — review","WITHIN typical range"))</f>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="36">
-        <f>D11</f>
-      </c>
-      <c r="D34" s="37">
+      <c r="C35" s="38">
+        <f>D13</f>
+      </c>
+      <c r="D35" s="39">
         <v>0.1</v>
       </c>
-      <c r="E34" s="37">
-        <v>0.25</v>
-      </c>
-      <c r="F34" s="38">
-        <f>IF(C34&lt;D34,"BELOW typical — investigate",IF(C34&gt;E34,"ABOVE typical — review","WITHIN typical range"))</f>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="36">
-        <f>D13</f>
-      </c>
-      <c r="D35" s="37">
-        <v>0.1</v>
-      </c>
-      <c r="E35" s="37">
+      <c r="E35" s="39">
         <v>0.2</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="40">
         <f>IF(C35&lt;D35,"BELOW typical — investigate",IF(C35&gt;E35,"ABOVE typical — review","WITHIN typical range"))</f>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C36" s="39">
+      <c r="B36" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="41">
         <f>D16</f>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="42">
         <v>1.5</v>
       </c>
-      <c r="E36" s="40">
+      <c r="E36" s="42">
         <v>2.2</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="40">
         <f>IF(C36&lt;D36,"BELOW typical — investigate",IF(C36&gt;E36,"ABOVE typical — review","WITHIN typical range"))</f>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
+      <c r="A38" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="41"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3254,7 +3342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3268,254 +3356,254 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>166</v>
+      <c r="B4" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>168</v>
+      <c r="B5" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>170</v>
+      <c r="B6" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>172</v>
+      <c r="B7" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>174</v>
+      <c r="B8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>176</v>
+      <c r="B9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>178</v>
+      <c r="B10" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>180</v>
+      <c r="B11" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>183</v>
+      <c r="B14" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>185</v>
+      <c r="B15" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>187</v>
+      <c r="B16" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>189</v>
+      <c r="B17" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>191</v>
+      <c r="B18" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="A20" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>194</v>
+      <c r="B21" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>196</v>
+      <c r="B22" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>198</v>
+      <c r="B23" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>200</v>
+      <c r="B24" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>202</v>
+      <c r="B25" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>204</v>
+      <c r="B26" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="A28" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>207</v>
+      <c r="B29" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>209</v>
+      <c r="B30" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="31" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>211</v>
+      <c r="B31" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>213</v>
+      <c r="B32" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="33" ht="50" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="44" t="s">
-        <v>214</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>215</v>
+      <c r="B33" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
